--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96876</v>
+        <v>96887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688354</v>
       </c>
       <c r="B3" t="n">
-        <v>80211</v>
+        <v>80215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688354</v>
       </c>
       <c r="B3" t="n">
-        <v>80215</v>
+        <v>80216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96888</v>
+        <v>96893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688354</v>
       </c>
       <c r="B3" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96893</v>
+        <v>96897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96897</v>
+        <v>96899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96899</v>
+        <v>96909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96909</v>
+        <v>96913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688354</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96913</v>
+        <v>96916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688354</v>
       </c>
       <c r="B3" t="n">
-        <v>80224</v>
+        <v>80227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96916</v>
+        <v>96917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688354</v>
       </c>
       <c r="B3" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52877-2025 artfynd.xlsx
+++ b/artfynd/A 52877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688355</v>
       </c>
       <c r="B2" t="n">
-        <v>96917</v>
+        <v>96934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688354</v>
       </c>
       <c r="B3" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
